--- a/toolkit/save-workshop-agenda.xlsx
+++ b/toolkit/save-workshop-agenda.xlsx
@@ -524,7 +524,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SAVE Workshop Agenda — 3-Day Template</t>
+          <t>VE Workshop Agenda — 3-Day Template</t>
         </is>
       </c>
     </row>
@@ -535,9 +535,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -560,6 +558,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -677,6 +676,7 @@
       <c r="C16" s="7" t="inlineStr"/>
       <c r="D16" s="7" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -810,6 +810,7 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -907,6 +908,7 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -1022,6 +1024,7 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr"/>
     </row>
+    <row r="47"/>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
@@ -1029,6 +1032,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
